--- a/data/trans_dic/P8_2_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P8_2_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a subir varios pisos</t>
+          <t>Población con limitación a subir varios pisos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,59; 14,71</t>
+          <t>8,75; 14,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,72; 16,84</t>
+          <t>9,9; 16,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,85</t>
+          <t>8,59; 14,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,85</t>
+          <t>6,7; 11,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 20,6</t>
+          <t>12,37; 20,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,65; 15,82</t>
+          <t>8,68; 16,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,12; 15,98</t>
+          <t>8,14; 15,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 14,51</t>
+          <t>9,61; 14,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,53; 15,58</t>
+          <t>10,92; 15,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 15,46</t>
+          <t>10,21; 15,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,07; 14,07</t>
+          <t>9,25; 14,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,47; 12,04</t>
+          <t>8,6; 11,77</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 12,34</t>
+          <t>6,09; 12,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,94; 14,62</t>
+          <t>8,02; 14,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,85; 14,48</t>
+          <t>7,56; 14,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 14,24</t>
+          <t>9,02; 14,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,51; 11,45</t>
+          <t>5,66; 11,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 15,15</t>
+          <t>7,97; 15,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 16,41</t>
+          <t>8,92; 16,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 17,33</t>
+          <t>12,02; 17,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 10,66</t>
+          <t>6,45; 10,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,7; 13,86</t>
+          <t>8,79; 13,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,1; 14,28</t>
+          <t>9,12; 14,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,03; 15,03</t>
+          <t>10,93; 15,07</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,38; 15,87</t>
+          <t>10,02; 15,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,43; 22,05</t>
+          <t>15,04; 21,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,51; 18,6</t>
+          <t>12,34; 18,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,62; 81,37</t>
+          <t>16,15; 79,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,21; 30,55</t>
+          <t>18,05; 31,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,71; 33,73</t>
+          <t>21,71; 33,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,39; 34,22</t>
+          <t>20,16; 35,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,05; 32,89</t>
+          <t>21,75; 32,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,73; 18,16</t>
+          <t>12,87; 18,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,06; 24,11</t>
+          <t>18,07; 23,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,47; 21,49</t>
+          <t>15,07; 21,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,95; 76,0</t>
+          <t>19,09; 73,83</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,67; 20,92</t>
+          <t>16,74; 21,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 21,19</t>
+          <t>16,16; 20,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,53; 18,83</t>
+          <t>14,5; 18,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,94; 21,95</t>
+          <t>16,8; 21,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,01; 22,83</t>
+          <t>17,34; 23,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,5; 18,98</t>
+          <t>13,35; 18,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,13; 18,09</t>
+          <t>12,77; 18,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 16,74</t>
+          <t>7,2; 16,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,69; 21,01</t>
+          <t>17,49; 21,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,63; 19,27</t>
+          <t>15,8; 19,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,47; 17,69</t>
+          <t>14,43; 17,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,54; 18,54</t>
+          <t>11,01; 18,48</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,54; 20,14</t>
+          <t>12,36; 20,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,15; 20,73</t>
+          <t>14,05; 20,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,12; 24,02</t>
+          <t>17,42; 23,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,12; 24,71</t>
+          <t>17,49; 24,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,45; 24,32</t>
+          <t>17,52; 24,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,47; 36,72</t>
+          <t>29,9; 36,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,45; 32,03</t>
+          <t>25,0; 31,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,96; 30,89</t>
+          <t>20,28; 31,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,24; 21,53</t>
+          <t>16,61; 21,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,16; 29,41</t>
+          <t>24,57; 29,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,23; 27,03</t>
+          <t>22,46; 27,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,4; 27,65</t>
+          <t>20,25; 27,4</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,06</t>
+          <t>1,87; 6,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,98</t>
+          <t>2,12; 7,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,48</t>
+          <t>0,77; 4,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,69</t>
+          <t>1,02; 4,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,66; 35,14</t>
+          <t>29,73; 35,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,4; 38,15</t>
+          <t>32,38; 38,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,11; 34,24</t>
+          <t>27,91; 34,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,96; 35,72</t>
+          <t>30,35; 36,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24,47; 29,06</t>
+          <t>24,63; 29,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,79; 31,95</t>
+          <t>26,87; 31,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,35; 27,75</t>
+          <t>22,55; 27,53</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,46; 28,36</t>
+          <t>23,28; 28,39</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,85; 15,24</t>
+          <t>12,77; 15,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,16; 16,86</t>
+          <t>14,51; 17,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,4; 15,79</t>
+          <t>13,32; 15,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,86; 39,2</t>
+          <t>14,8; 37,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,78; 24,7</t>
+          <t>21,74; 24,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,09; 27,21</t>
+          <t>24,21; 27,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,26; 24,23</t>
+          <t>21,24; 24,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,29; 23,08</t>
+          <t>17,31; 22,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,7; 19,6</t>
+          <t>17,7; 19,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,67; 21,73</t>
+          <t>19,69; 21,69</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,68; 19,63</t>
+          <t>17,78; 19,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,86; 32,25</t>
+          <t>18,02; 31,21</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a subir varios pisos</t>
+          <t>Población con limitación a subir varios pisos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40693; 69708</t>
+          <t>41472; 70329</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42489; 73644</t>
+          <t>43291; 73103</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36964; 63707</t>
+          <t>36844; 62545</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33262; 54752</t>
+          <t>33819; 56834</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>37197; 63189</t>
+          <t>37936; 63119</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27211; 49738</t>
+          <t>27287; 51982</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28166; 55466</t>
+          <t>28238; 53890</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42883; 64945</t>
+          <t>42996; 63610</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>82189; 121619</t>
+          <t>85192; 121236</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77291; 116229</t>
+          <t>76769; 117080</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70429; 109192</t>
+          <t>71809; 109181</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>80619; 114596</t>
+          <t>81846; 112004</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21804; 45291</t>
+          <t>22334; 45018</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33018; 60795</t>
+          <t>33349; 61022</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29602; 54618</t>
+          <t>28507; 53107</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39742; 64414</t>
+          <t>40775; 65802</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20492; 42589</t>
+          <t>21044; 42555</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27143; 51203</t>
+          <t>26947; 50782</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32697; 61086</t>
+          <t>33221; 59924</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45222; 66295</t>
+          <t>45981; 67320</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48228; 78741</t>
+          <t>47676; 78445</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65605; 104499</t>
+          <t>66262; 102242</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68208; 107031</t>
+          <t>68324; 106489</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92079; 125494</t>
+          <t>91217; 125782</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56315; 86083</t>
+          <t>54371; 85959</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>96962; 138539</t>
+          <t>94509; 136000</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65296; 97089</t>
+          <t>64394; 97636</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111054; 543760</t>
+          <t>107905; 528625</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28883; 51257</t>
+          <t>30278; 52175</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56476; 87732</t>
+          <t>56484; 86577</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32218; 56847</t>
+          <t>33497; 58805</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36807; 54897</t>
+          <t>36298; 54163</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>90402; 129002</t>
+          <t>91382; 130914</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>160433; 214245</t>
+          <t>160581; 211481</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>106441; 147831</t>
+          <t>103667; 147429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>158280; 634762</t>
+          <t>159456; 616628</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>206467; 259095</t>
+          <t>207282; 262598</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>189977; 245537</t>
+          <t>187348; 243074</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>167058; 216446</t>
+          <t>166726; 217667</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>175342; 227180</t>
+          <t>173868; 226110</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>121528; 163062</t>
+          <t>123868; 168674</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>103525; 145539</t>
+          <t>102372; 144201</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>108403; 149440</t>
+          <t>105431; 149545</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61704; 163750</t>
+          <t>70383; 163655</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>345408; 410193</t>
+          <t>341526; 414139</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>301033; 371142</t>
+          <t>304221; 374507</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>285822; 349510</t>
+          <t>285120; 351711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>232302; 373157</t>
+          <t>221622; 372065</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43957; 70594</t>
+          <t>43333; 70287</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>72267; 105861</t>
+          <t>71728; 106634</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106240; 149079</t>
+          <t>108138; 146812</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81318; 117372</t>
+          <t>83074; 117318</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>99246; 138300</t>
+          <t>99655; 137609</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>224435; 279663</t>
+          <t>227720; 280026</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>187909; 236476</t>
+          <t>184563; 235465</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>159546; 259893</t>
+          <t>170597; 263710</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>149254; 197942</t>
+          <t>152713; 201792</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>307299; 374109</t>
+          <t>312576; 373708</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>302095; 367258</t>
+          <t>305249; 368904</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>268520; 363952</t>
+          <t>266578; 360737</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5420; 18082</t>
+          <t>5579; 17989</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5198; 18623</t>
+          <t>5667; 19824</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2137; 12856</t>
+          <t>2206; 13713</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2547; 11278</t>
+          <t>2444; 11946</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>370393; 438822</t>
+          <t>371318; 437130</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>359112; 422801</t>
+          <t>358825; 424819</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>304165; 370445</t>
+          <t>301984; 369557</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>227942; 271721</t>
+          <t>230927; 275044</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>378596; 449579</t>
+          <t>381058; 450847</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>368397; 439397</t>
+          <t>369568; 436282</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>306033; 379975</t>
+          <t>308763; 377000</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>234930; 284012</t>
+          <t>233056; 284304</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>420192; 498256</t>
+          <t>417562; 496278</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>484117; 576433</t>
+          <t>496054; 584193</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>453626; 534574</t>
+          <t>451056; 532709</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>501677; 1323120</t>
+          <t>499416; 1277518</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>735678; 834466</t>
+          <t>734418; 831775</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>855023; 965690</t>
+          <t>859191; 966098</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>750830; 855655</t>
+          <t>750014; 852900</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>618370; 825742</t>
+          <t>619077; 821482</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1176420; 1303031</t>
+          <t>1176954; 1299212</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1370480; 1514082</t>
+          <t>1371490; 1511362</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1223042; 1358061</t>
+          <t>1229677; 1359942</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1241521; 2242448</t>
+          <t>1253187; 2170199</t>
         </is>
       </c>
     </row>
